--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,0</t>
+          <t>-1,07; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,0</t>
+          <t>-1,07; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,65</t>
+          <t>0,53; 5,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,36</t>
+          <t>-0,22; 0,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,34</t>
+          <t>0,01; 2,32</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,17</t>
+          <t>-1,5; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,28</t>
+          <t>-0,44; 3,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,57</t>
+          <t>-0,63; 0,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,21</t>
+          <t>0,2; 2,09</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 224,74</t>
+          <t>-78,86; 306,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,43; 580,07</t>
+          <t>-33,28; 597,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 257,74</t>
+          <t>-79,25; 302,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 758,56</t>
+          <t>4,36; 759,26</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,71</t>
+          <t>-0,69; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,63</t>
+          <t>1,36; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,99</t>
+          <t>-2,24; 0,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,98</t>
+          <t>-0,73; 3,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,42</t>
+          <t>-1,32; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,3</t>
+          <t>0,75; 3,36</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106,04; 2967,95</t>
+          <t>114,55; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 49,7</t>
+          <t>-60,65; 53,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 156,01</t>
+          <t>-21,07; 153,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 42,19</t>
+          <t>-58,93; 47,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,43; 261,76</t>
+          <t>30,09; 294,46</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,94</t>
+          <t>-1,53; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,76</t>
+          <t>-1,01; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,88</t>
+          <t>-2,81; 2,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,41</t>
+          <t>2,78; 8,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,56</t>
+          <t>-1,47; 1,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,96</t>
+          <t>0,47; 6,15</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 164,04</t>
+          <t>-55,49; 148,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 350,67</t>
+          <t>-28,17; 332,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 63,87</t>
+          <t>-38,72; 64,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,97; 205,5</t>
+          <t>36,2; 193,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 47,62</t>
+          <t>-30,83; 56,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,91; 177,98</t>
+          <t>17,47; 193,12</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,71</t>
+          <t>-1,16; 4,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,94</t>
+          <t>2,87; 8,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 4,89</t>
+          <t>-4,55; 4,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 7,34</t>
+          <t>-1,22; 7,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,64</t>
+          <t>-2,08; 3,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,48</t>
+          <t>1,56; 6,65</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,4; 220,7</t>
+          <t>-27,83; 193,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47,76; 349,79</t>
+          <t>53,82; 375,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 40,33</t>
+          <t>-26,37; 38,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 60,2</t>
+          <t>-6,99; 58,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 47,88</t>
+          <t>-20,11; 47,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,64; 86,63</t>
+          <t>14,08; 90,62</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -1,91</t>
+          <t>-11,93; -2,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 3,86</t>
+          <t>-5,74; 3,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,61</t>
+          <t>-4,01; 7,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 7,48</t>
+          <t>-13,78; 7,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,52</t>
+          <t>-6,21; 1,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,99</t>
+          <t>-10,16; 4,28</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,21; -17,09</t>
+          <t>-71,47; -19,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 38,18</t>
+          <t>-34,14; 34,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 48,55</t>
+          <t>-18,47; 50,18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 40,96</t>
+          <t>-61,17; 44,36</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 11,57</t>
+          <t>-32,93; 11,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 25,0</t>
+          <t>-51,03; 27,77</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 3,59</t>
+          <t>-9,92; 4,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 14,33</t>
+          <t>1,04; 14,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -0,94</t>
+          <t>-15,07; -1,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,45; 16,45</t>
+          <t>4,04; 15,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,32; -1,22</t>
+          <t>-11,38; -1,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,64; 13,67</t>
+          <t>4,57; 13,66</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 22,51</t>
+          <t>-41,73; 27,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,82; 87,4</t>
+          <t>4,25; 95,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,46; -1,64</t>
+          <t>-40,79; -3,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,92; 53,4</t>
+          <t>10,67; 52,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,07; -4,7</t>
+          <t>-35,84; -5,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,57; 53,98</t>
+          <t>14,29; 54,78</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,46</t>
+          <t>-1,27; 0,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,26</t>
+          <t>1,58; 4,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,14</t>
+          <t>-1,62; 1,25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,33</t>
+          <t>1,94; 6,27</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,54</t>
+          <t>-1,19; 0,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,01</t>
+          <t>2,5; 5,06</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 15,34</t>
+          <t>-31,62; 18,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>36,77; 134,22</t>
+          <t>43,31; 140,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 13,27</t>
+          <t>-16,7; 14,98</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,52; 72,53</t>
+          <t>22,68; 72,69</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 8,71</t>
+          <t>-17,1; 7,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,56; 82,08</t>
+          <t>37,83; 83,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Edad-trans_camb.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,0</t>
+          <t>-1,09; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,42</t>
+          <t>-0,31; 0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,32</t>
+          <t>0,04; 2,11</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>722,8%</t>
+          <t>701,27%</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,17</t>
+          <t>-1,51; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,17</t>
+          <t>0,03; 3,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,59</t>
+          <t>-0,69; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,09</t>
+          <t>0,3; 2,13</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111,73%</t>
+          <t>138,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>192,48%</t>
+          <t>207,13%</t>
         </is>
       </c>
     </row>
@@ -873,22 +873,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 306,41</t>
+          <t>-78,5; 280,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 597,86</t>
+          <t>-21,67; 619,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 302,82</t>
+          <t>-79,54; 245,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 759,26</t>
+          <t>11,86; 792,78</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,77</t>
+          <t>-0,68; 0,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,55</t>
+          <t>1,07; 4,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,98</t>
+          <t>-2,28; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,07</t>
+          <t>-0,27; 3,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,55</t>
+          <t>-1,33; 0,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,36</t>
+          <t>0,79; 3,27</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>641,1%</t>
+          <t>579,58%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>117,24%</t>
+          <t>120,2%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114,55; —</t>
+          <t>56,43; 2466,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 53,22</t>
+          <t>-60,31; 60,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 153,53</t>
+          <t>-8,58; 180,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 47,21</t>
+          <t>-57,97; 51,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,09; 294,46</t>
+          <t>25,77; 279,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>4,78</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,77</t>
+          <t>-1,55; 1,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,78</t>
+          <t>1,63; 6,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,78</t>
+          <t>-2,63; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,84</t>
+          <t>3,13; 8,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,81</t>
+          <t>-1,6; 1,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,15</t>
+          <t>2,97; 6,49</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105,97%</t>
+          <t>175,9%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102,91%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>119,65%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 148,56</t>
+          <t>-54,88; 157,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 332,2</t>
+          <t>40,55; 477,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 64,73</t>
+          <t>-37,86; 68,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,2; 193,32</t>
+          <t>35,4; 187,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 56,46</t>
+          <t>-32,62; 52,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,47; 193,12</t>
+          <t>59,05; 204,9</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>4,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,33</t>
+          <t>-1,11; 4,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,08</t>
+          <t>2,33; 8,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,75</t>
+          <t>-4,38; 5,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,01</t>
+          <t>-1,21; 7,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,7</t>
+          <t>-1,83; 3,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,65</t>
+          <t>1,41; 6,44</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>157,09%</t>
+          <t>151,77%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 193,82</t>
+          <t>-27,03; 199,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>53,82; 375,41</t>
+          <t>43,76; 378,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 38,88</t>
+          <t>-25,51; 43,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 58,86</t>
+          <t>-7,13; 63,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 47,0</t>
+          <t>-17,81; 52,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,08; 90,62</t>
+          <t>13,58; 85,31</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>6,47</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -2,07</t>
+          <t>-11,58; -1,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 3,69</t>
+          <t>-6,56; 3,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 7,9</t>
+          <t>-4,23; 7,99</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 7,86</t>
+          <t>1,06; 11,61</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,59</t>
+          <t>-6,41; 1,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 4,28</t>
+          <t>-0,88; 6,1</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-4,65%</t>
+          <t>-10,1%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-12,49%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-7,42%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,47; -19,1</t>
+          <t>-70,9; -16,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 34,63</t>
+          <t>-38,63; 28,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 50,18</t>
+          <t>-19,21; 48,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 44,36</t>
+          <t>4,7; 74,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 11,96</t>
+          <t>-34,32; 9,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,03; 27,77</t>
+          <t>-4,58; 43,0</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>10,34</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 4,24</t>
+          <t>-9,29; 4,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,04; 14,16</t>
+          <t>0,62; 14,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -1,0</t>
+          <t>-14,77; -1,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,85</t>
+          <t>4,62; 16,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,46</t>
+          <t>-11,73; -0,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,57; 13,66</t>
+          <t>4,66; 13,66</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 27,07</t>
+          <t>-39,95; 26,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,25; 95,37</t>
+          <t>1,9; 93,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -3,27</t>
+          <t>-39,91; -4,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,67; 52,15</t>
+          <t>12,26; 55,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -5,66</t>
+          <t>-36,68; -2,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,29; 54,78</t>
+          <t>14,42; 53,68</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,53</t>
+          <t>-1,4; 0,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,26</t>
+          <t>2,48; 4,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,25</t>
+          <t>-1,81; 1,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,27</t>
+          <t>4,38; 7,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,46</t>
+          <t>-1,24; 0,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,06</t>
+          <t>3,79; 5,59</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 18,63</t>
+          <t>-34,02; 16,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43,31; 140,62</t>
+          <t>59,07; 148,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 14,98</t>
+          <t>-17,81; 14,7</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,68; 72,69</t>
+          <t>42,01; 84,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 7,62</t>
+          <t>-17,89; 7,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,83; 83,86</t>
+          <t>54,68; 92,21</t>
         </is>
       </c>
     </row>
